--- a/Dentists/web/public/resources/principal/principal-extraction-model.xlsx
+++ b/Dentists/web/public/resources/principal/principal-extraction-model.xlsx
@@ -35,10 +35,9 @@
     <definedName name="CtMainRate">Rates!$B$21</definedName>
     <definedName name="CtSmallThresh">Rates!$B$22</definedName>
     <definedName name="CtMainThresh">Rates!$B$23</definedName>
-    <definedName name="Class2Weekly">Rates!$B$24</definedName>
-    <definedName name="Class2Threshold">Rates!$B$25</definedName>
-    <definedName name="LtdSalary">Rates!$B$26</definedName>
-    <definedName name="LtdAdminCost">Rates!$B$27</definedName>
+    <definedName name="Class2Charge">Rates!$B$24</definedName>
+    <definedName name="LtdSalary">Rates!$B$25</definedName>
+    <definedName name="LtdAdminCost">Rates!$B$26</definedName>
     <definedName name="In_Profit">'Your figures'!$B$3</definedName>
     <definedName name="In_Pension">'Your figures'!$B$4</definedName>
     <definedName name="P_TaxableProfit">'Your figures'!$E$3</definedName>
@@ -64,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="74">
   <si>
     <t>Locked rates: do not edit (2026/27)</t>
   </si>
@@ -135,10 +134,7 @@
     <t>Corporation Tax: main rate lower limit (GBP)</t>
   </si>
   <si>
-    <t>Class 2 NI: weekly amount (GBP)</t>
-  </si>
-  <si>
-    <t>Class 2 NI: small profits threshold (GBP)</t>
+    <t>Class 2 NI: weekly amount (removed from 6 Apr 2024)</t>
   </si>
   <si>
     <t>Ltd: director salary (GBP)</t>
@@ -276,7 +272,7 @@
     <t>Partnership model: sole trader or single principal, no Class 1 NI on profit.</t>
   </si>
   <si>
-    <t>Class 2 NI at GBP3.45/week if profit above GBP6,725.</t>
+    <t>Class 2 NI: not payable. The liability was removed from 6 April 2024.</t>
   </si>
   <si>
     <t>NHS Pension: the model does not quantify the accrual you would lose on</t>
@@ -745,7 +741,7 @@
   <sheetPr>
     <tabColor rgb="FF001b3d"/>
   </sheetPr>
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="54" style="1" customWidth="1"/>
@@ -939,7 +935,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="4">
-        <v>3.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -947,7 +943,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="4">
-        <v>6725</v>
+        <v>12570</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -955,14 +951,6 @@
         <v>25</v>
       </c>
       <c r="B26" s="4">
-        <v>12570</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B27" s="4">
         <v>2500</v>
       </c>
     </row>
@@ -996,33 +984,33 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B1" s="6"/>
       <c r="D1" s="7" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E1" s="7"/>
       <c r="G1" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H1" s="6"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B3" s="9">
         <v>120000</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E3" s="10">
         <f>MAX(0,In_Profit-In_Pension)</f>
       </c>
       <c r="G3" s="8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H3" s="10">
         <f>LtdSalary</f>
@@ -1030,19 +1018,19 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B4" s="9">
         <v>0</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E4" s="10">
         <f>LET(tp,P_TaxableProfit,pa,IF(tp&gt;100000,MAX(0,PA-(tp-100000)/2),PA),t,MAX(0,tp-pa),basic,MIN(t,BasicLimit-PA),higher,MAX(0,MIN(t-basic,HigherLimit-BasicLimit)),additional,MAX(0,t-basic-higher),basic*IncomeBasic+higher*IncomeHigher+additional*IncomeAdditional)</f>
       </c>
       <c r="G4" s="8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H4" s="10">
         <f>MAX(0,(L_Salary-NiSecondary)*EmployerNiRate)</f>
@@ -1050,13 +1038,13 @@
     </row>
     <row r="5" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D5" s="8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E5" s="10">
         <f>IF(P_TaxableProfit&lt;=Class4Lower,0,(MIN(P_TaxableProfit,Class4Upper)-Class4Lower)*Class4LowerRate+MAX(0,P_TaxableProfit-Class4Upper)*Class4UpperRate)</f>
       </c>
       <c r="G5" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H5" s="10">
         <f>MAX(0,In_Profit-L_Salary-L_EmployerNi-In_Pension)</f>
@@ -1064,13 +1052,13 @@
     </row>
     <row r="6" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D6" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="E6" s="10">
+        <f>Class2Charge</f>
+      </c>
+      <c r="G6" s="8" t="s">
         <v>38</v>
-      </c>
-      <c r="E6" s="10">
-        <f>IF(In_Profit&gt;Class2Threshold,52*Class2Weekly,0)</f>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>39</v>
       </c>
       <c r="H6" s="10">
         <f>IF(L_ProfitAfterSalary&lt;=0,0,IF(L_ProfitAfterSalary&lt;=CtSmallThresh,L_ProfitAfterSalary*CtSmallRate,IF(L_ProfitAfterSalary&gt;=CtMainThresh,L_ProfitAfterSalary*CtMainRate,CtSmallThresh*CtSmallRate+(L_ProfitAfterSalary-CtSmallThresh)*0.265)))</f>
@@ -1078,13 +1066,13 @@
     </row>
     <row r="7" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D7" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E7" s="12">
         <f>P_IncomeTax+P_Class4+P_Class2</f>
       </c>
       <c r="G7" s="8" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H7" s="10">
         <f>MAX(0,L_ProfitAfterSalary-L_CorpTax)</f>
@@ -1092,13 +1080,13 @@
     </row>
     <row r="8" spans="4:8" x14ac:dyDescent="0.25">
       <c r="D8" s="13" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E8" s="14">
         <f>In_Profit-P_TotalTax</f>
       </c>
       <c r="G8" s="8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H8" s="10">
         <f>IF(L_Salary&lt;=NiPrimary,0,(MIN(L_Salary,50270)-NiPrimary)*EmployeeNiRate+MAX(0,L_Salary-50270)*0.02)</f>
@@ -1106,7 +1094,7 @@
     </row>
     <row r="9" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G9" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H9" s="10">
         <f>LET(sal,L_Salary,pa,IF(sal&gt;100000,MAX(0,PA-(sal-100000)/2),PA),t,MAX(0,sal-pa),basic,MIN(t,BasicLimit-PA),higher,MAX(0,MIN(t-basic,HigherLimit-BasicLimit)),additional,MAX(0,t-basic-higher),basic*IncomeBasic+higher*IncomeHigher+additional*IncomeAdditional)</f>
@@ -1114,13 +1102,13 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B10">
         <f>IF(ABS(P_Net+P_TotalTax-In_Profit)&lt;0.1,"OK","ERROR")</f>
       </c>
       <c r="G10" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H10" s="10">
         <f>IF(L_Dividend&lt;=0,0,LET(sal,L_Salary,div,L_Dividend,pa,IF(sal+div&gt;100000,MAX(0,PA-(sal+div-100000)/2),PA),paUsedBySal,MIN(sal,pa),paLeft,MAX(0,pa-paUsedBySal),taxableDiv,MAX(0,div-paLeft-DivAllowance),basicBand,BasicLimit-PA,higherBand,HigherLimit-BasicLimit,salInBasic,MIN(MAX(0,sal-pa),basicBand),salInHigher,MIN(MAX(0,sal-pa-salInBasic),higherBand),remBasic,MAX(0,basicBand-salInBasic),remHigher,MAX(0,higherBand-salInHigher),inBasic,MIN(taxableDiv,remBasic),inHigher,MIN(taxableDiv-inBasic,remHigher),inAdd,MAX(0,taxableDiv-inBasic-inHigher),inBasic*DivBasic+inHigher*DivHigher+inAdd*DivAdditional))</f>
@@ -1128,13 +1116,13 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B11">
         <f>IF(ABS(L_Net+L_TotalCost-In_Profit)&lt;0.1,"OK","ERROR")</f>
       </c>
       <c r="G11" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H11" s="10">
         <f>LtdAdminCost</f>
@@ -1142,7 +1130,7 @@
     </row>
     <row r="12" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G12" s="11" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H12" s="12">
         <f>L_SalaryTax+L_EmployeeNi+L_EmployerNi+L_CorpTax+L_DivTax+L_AdminCost</f>
@@ -1150,7 +1138,7 @@
     </row>
     <row r="13" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G13" s="13" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H13" s="14">
         <f>L_Salary-L_SalaryTax-L_EmployeeNi+(L_Dividend-L_DivTax)-L_AdminCost+In_Pension</f>
@@ -1158,7 +1146,7 @@
     </row>
     <row r="15" spans="7:8" x14ac:dyDescent="0.25">
       <c r="G15" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H15" s="10">
         <f>P_Net-L_Net</f>
@@ -1188,72 +1176,72 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -1272,87 +1260,87 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
